--- a/www/download/IND.surplus_value.empe_hs.r.pc.rpPE.xlsx
+++ b/www/download/IND.surplus_value.empe_hs.r.pc.rpPE.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-7.48</t>
+          <t>-0.0747582006515491</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-15.67</t>
+          <t>-0.156717635696669</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-16.09</t>
+          <t>-0.160852562312858</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-0.0331840068070641</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-5.39</t>
+          <t>-0.0538700861594689</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>0.0219545631392239</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>0.0675150637024735</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>0.017976887594443</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-14.68</t>
+          <t>-0.146788264114035</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-22.78</t>
+          <t>-0.227764352868932</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-25.86</t>
+          <t>-0.258568691286812</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>-26.29</t>
+          <t>-0.262933269629239</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-30.33</t>
+          <t>-0.303294169917029</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-27.03</t>
+          <t>-0.270294078076372</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-23.97</t>
+          <t>-0.239657310910418</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-52.28</t>
+          <t>-0.522837028666779</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-49.28</t>
+          <t>-0.492773658731231</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-40.98</t>
+          <t>-0.409801070022859</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-40.51</t>
+          <t>-0.405057302867474</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-35.88</t>
+          <t>-0.358771442295083</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-25.92</t>
+          <t>-0.25917162691958</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-25.5</t>
+          <t>-0.255008006677536</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-29.95</t>
+          <t>-0.299517246429911</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-37.31</t>
+          <t>-0.373117319372487</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-40.53</t>
+          <t>-0.405348468617896</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-39.72</t>
+          <t>-0.397204570219648</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-40.53</t>
+          <t>-0.405254251571023</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-42.42</t>
+          <t>-0.424219227871447</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>-45.35</t>
+          <t>-0.4534856771336</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>-45.57</t>
+          <t>-0.455717620089561</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-56.8</t>
+          <t>-0.568016785904564</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-54.13</t>
+          <t>-0.541308197350857</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-48.77</t>
+          <t>-0.487740902699892</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-48.37</t>
+          <t>-0.483685109768991</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-45.73</t>
+          <t>-0.457279264187362</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-37.53</t>
+          <t>-0.375308436900433</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-39.31</t>
+          <t>-0.393071161071465</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-43.34</t>
+          <t>-0.433376104019217</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-48.08</t>
+          <t>-0.480810875421085</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-52.76</t>
+          <t>-0.527583231959458</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-51.79</t>
+          <t>-0.517873936346793</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-51.81</t>
+          <t>-0.518120784742687</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-52.71</t>
+          <t>-0.527089021159156</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-53.04</t>
+          <t>-0.530364958000509</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-53.39</t>
+          <t>-0.533928597772941</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1060.74</t>
+          <t>10.6074061032321</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1253.12</t>
+          <t>12.5312151256863</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1592.21</t>
+          <t>15.9221396530235</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>973.41</t>
+          <t>9.73408765010398</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>967.94</t>
+          <t>9.67941140463464</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>943.65</t>
+          <t>9.43646253746408</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>815.64</t>
+          <t>8.15635404243955</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>692.75</t>
+          <t>6.92747118163652</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>743.98</t>
+          <t>7.43980030694823</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>538.53</t>
+          <t>5.38530609089141</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>519.28</t>
+          <t>5.19277986395489</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>501.43</t>
+          <t>5.01427765397224</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>438.74</t>
+          <t>4.38740034858636</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>339.07</t>
+          <t>3.39069137635291</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>318.7</t>
+          <t>3.18695985970476</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>86.69</t>
+          <t>0.866923370417882</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>73.39</t>
+          <t>0.733931157289646</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>76.58</t>
+          <t>0.765783737774908</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>0.797340515067336</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>179.43</t>
+          <t>1.79432477692378</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>186.23</t>
+          <t>1.862259898808</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>231.92</t>
+          <t>2.319203749591</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>280.46</t>
+          <t>2.8045979686354</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>296.34</t>
+          <t>2.96335348141433</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>291.44</t>
+          <t>2.91437338007333</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>215.41</t>
+          <t>2.15413110688574</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>182.26</t>
+          <t>1.82264926592344</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>161.8</t>
+          <t>1.6180491339213</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>142.41</t>
+          <t>1.42405571260221</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>139.65</t>
+          <t>1.39646238487312</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>0.136362254820025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>0.0938201366847249</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>0.0244904510632171</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>0.0693540317769452</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>0.0743383501767068</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>0.0290004170368534</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.00876750930951165</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.00130107642107302</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>-8.6</t>
+          <t>-0.0860485273077443</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-9.84</t>
+          <t>-0.0984403491618433</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>-14.58</t>
+          <t>-0.145833632417446</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>-20.49</t>
+          <t>-0.204942162839251</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>-18.87</t>
+          <t>-0.188711042348498</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>-16.48</t>
+          <t>-0.164848733837454</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>-10.67</t>
+          <t>-0.106698941548211</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1433.01</t>
+          <t>14.3300658495124</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1283.12</t>
+          <t>12.8311536190073</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1084.96</t>
+          <t>10.8496490657864</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>978.63</t>
+          <t>9.78634780823155</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>930.95</t>
+          <t>9.30948432935327</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>851.21</t>
+          <t>8.51212280879507</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>819.07</t>
+          <t>8.19068509832671</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>805.58</t>
+          <t>8.05577732672925</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>779.77</t>
+          <t>7.79766966470915</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>789.14</t>
+          <t>7.89136282907383</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>744.37</t>
+          <t>7.44374334616871</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>647.09</t>
+          <t>6.47091748944379</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>576.22</t>
+          <t>5.76215088139514</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>476.07</t>
+          <t>4.76069192305699</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>422.39</t>
+          <t>4.22385661816843</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>39.17</t>
+          <t>0.39174061865908</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>41.26</t>
+          <t>0.412627775671541</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>43.62</t>
+          <t>0.436207969850558</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>37.16</t>
+          <t>0.37159561346491</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>43.92</t>
+          <t>0.439161398534408</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>56.16</t>
+          <t>0.561586824039254</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>56.48</t>
+          <t>0.564807756777151</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>0.436982699384403</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>20.72</t>
+          <t>0.207150608415376</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>0.0769674379395862</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>0.0806215457459314</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>0.0953705664074949</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>0.106844707099763</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>0.0934747679673964</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>0.0906821617257361</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>461.58</t>
+          <t>4.61581598182508</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>282.48</t>
+          <t>2.82481574039148</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>305.35</t>
+          <t>3.05346395285095</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>287.94</t>
+          <t>2.87938131767309</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>308.63</t>
+          <t>3.0862561859643</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>332.77</t>
+          <t>3.3276878622429</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>261.58</t>
+          <t>2.61582304732271</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>190.24</t>
+          <t>1.9023998645494</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>166.06</t>
+          <t>1.66064755677908</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>128.95</t>
+          <t>1.28948704057457</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>116.03</t>
+          <t>1.160271664386</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>100.09</t>
+          <t>1.00094213262058</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>84.54</t>
+          <t>0.845443064300453</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>63.49</t>
+          <t>0.634877514660851</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>78.46</t>
+          <t>0.784649686453427</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-49.07</t>
+          <t>-0.49069080221178</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-47.34</t>
+          <t>-0.473361889281543</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-41.52</t>
+          <t>-0.415211349385859</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-40.31</t>
+          <t>-0.403134348340515</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-35.38</t>
+          <t>-0.353800573069563</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-28.2</t>
+          <t>-0.281960870100555</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-29.13</t>
+          <t>-0.291337972873889</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-33.88</t>
+          <t>-0.338768408428446</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>-42.9</t>
+          <t>-0.429008496591339</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-42.4</t>
+          <t>-0.423979658626708</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>-40.66</t>
+          <t>-0.406566559362913</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>-40.97</t>
+          <t>-0.409678673157626</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>-41.21</t>
+          <t>-0.412058294365712</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>-42.53</t>
+          <t>-0.425330887649326</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>-43.55</t>
+          <t>-0.435454441799044</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-35.95</t>
+          <t>-0.359529086587453</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-35.02</t>
+          <t>-0.35021416546886</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>-27.17</t>
+          <t>-0.271696203121514</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-28.86</t>
+          <t>-0.288634150801343</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-25.4</t>
+          <t>-0.254043756592795</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-17</t>
+          <t>-0.169954309634006</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-19.57</t>
+          <t>-0.195691615729332</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-25.29</t>
+          <t>-0.252879377216761</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>-37.21</t>
+          <t>-0.372071408364011</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-39.75</t>
+          <t>-0.39751028340853</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>-37.86</t>
+          <t>-0.378647169356115</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>-37.42</t>
+          <t>-0.374200420878622</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>-40.23</t>
+          <t>-0.402297073063483</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>-41.4</t>
+          <t>-0.414041174172991</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>-43.78</t>
+          <t>-0.437764652496131</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-18.66</t>
+          <t>-0.186622123351465</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-16.84</t>
+          <t>-0.168402524726333</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>-6.3</t>
+          <t>-0.0629914822362037</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-0.0433201870115424</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>0.032170745536414</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>0.228003747343914</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>19.16</t>
+          <t>0.19164754121372</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>11.01</t>
+          <t>0.110069787337133</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.00765493420968122</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-0.0858978026613323</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>-6.52</t>
+          <t>-0.0651576716370508</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-0.0584791584376148</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>-9.53</t>
+          <t>-0.0953063535866328</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>-13.97</t>
+          <t>-0.139738408901628</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>-15.55</t>
+          <t>-0.155533182950752</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>708.36</t>
+          <t>7.08360668363013</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>575.36</t>
+          <t>5.75355291938252</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>539.47</t>
+          <t>5.39471007319264</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>462.07</t>
+          <t>4.62067036122214</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>443.56</t>
+          <t>4.43557570373293</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>449.31</t>
+          <t>4.49313970818126</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>433.2</t>
+          <t>4.33200880022812</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>375.83</t>
+          <t>3.75833342011289</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>290.86</t>
+          <t>2.90863971694651</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>238.27</t>
+          <t>2.38269106179328</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>229.34</t>
+          <t>2.29338250081369</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>202.09</t>
+          <t>2.02092280867826</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>159.69</t>
+          <t>1.59689806555872</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>131.82</t>
+          <t>1.31824054627684</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>129.41</t>
+          <t>1.29408771825296</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-21.37</t>
+          <t>-0.213728191177359</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-17.98</t>
+          <t>-0.179815492085926</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>-9.47</t>
+          <t>-0.0946529786145306</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-12.13</t>
+          <t>-0.12131606051125</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-8.58</t>
+          <t>-0.0857597768783506</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.00577848027141625</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-0.0247494208832392</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-0.0804491884176869</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-18.79</t>
+          <t>-0.187864114545629</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-25.9</t>
+          <t>-0.259023333554228</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-25.85</t>
+          <t>-0.258521694618601</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>-25.81</t>
+          <t>-0.258141866417734</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>-28.57</t>
+          <t>-0.285727764112917</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>-32.06</t>
+          <t>-0.320551559783112</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>-33.84</t>
+          <t>-0.338381333523217</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-48.23</t>
+          <t>-0.482346523306865</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-47.05</t>
+          <t>-0.470497576336099</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>-39.15</t>
+          <t>-0.391493124122983</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-39.45</t>
+          <t>-0.394491717040667</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-34.48</t>
+          <t>-0.344845696565318</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-27.79</t>
+          <t>-0.277901737692456</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-29.31</t>
+          <t>-0.293117315336706</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-34.62</t>
+          <t>-0.346158117769605</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>-39.91</t>
+          <t>-0.399093805320748</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-44.55</t>
+          <t>-0.445463715842098</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>-42.71</t>
+          <t>-0.427138306494265</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>-42.2</t>
+          <t>-0.422003313535039</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>-42.65</t>
+          <t>-0.426522297593097</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>-44.02</t>
+          <t>-0.44019055944294</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>-43.67</t>
+          <t>-0.43671466355661</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-7.4</t>
+          <t>-0.0740308617747474</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-9.32</t>
+          <t>-0.0931843165469396</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>-17.01</t>
+          <t>-0.170074101586921</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-23.12</t>
+          <t>-0.231202090045584</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-20.89</t>
+          <t>-0.208915177390288</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-20.17</t>
+          <t>-0.201728216838876</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-20.96</t>
+          <t>-0.209645345598065</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-25.59</t>
+          <t>-0.255917580741005</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>-32.97</t>
+          <t>-0.329701554633216</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-37.44</t>
+          <t>-0.37444789173483</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>-36.32</t>
+          <t>-0.363219052707929</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>-36.8</t>
+          <t>-0.367952706722138</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>-38.06</t>
+          <t>-0.380565015745412</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>-30.8</t>
+          <t>-0.308006876566602</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>-21.01</t>
+          <t>-0.210140158544696</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>57.29</t>
+          <t>0.572913252290895</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>52.33</t>
+          <t>0.523260379677811</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>43.87</t>
+          <t>0.438711055670031</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>51.91</t>
+          <t>0.519079351001408</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>54.22</t>
+          <t>0.542207977571938</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>0.742951876243602</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>66.29</t>
+          <t>0.662869382534395</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>45.13</t>
+          <t>0.451270564150909</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>24.06</t>
+          <t>0.240621754213463</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>16.48</t>
+          <t>0.164761094624255</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>17.14</t>
+          <t>0.171394338104334</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>26.65</t>
+          <t>0.266471120070481</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>0.194412882206199</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>10.97</t>
+          <t>0.109719150406666</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>0.0340560624132953</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>263.23</t>
+          <t>2.63230517730223</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>265.98</t>
+          <t>2.65976669149709</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>260.26</t>
+          <t>2.6025705375916</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>261.23</t>
+          <t>2.61232897970607</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>287.74</t>
+          <t>2.8774056946844</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>287.86</t>
+          <t>2.87860361910582</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>235.17</t>
+          <t>2.35170812408099</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>167.66</t>
+          <t>1.6766012561673</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>147.72</t>
+          <t>1.47718391115039</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>0.990027290626295</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>91.23</t>
+          <t>0.912308287893766</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>100.9</t>
+          <t>1.00901254997914</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>80.09</t>
+          <t>0.800919609457895</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>73.56</t>
+          <t>0.735571254567691</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>102.57</t>
+          <t>1.02568859029999</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>565.83</t>
+          <t>5.65833306968085</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>632.52</t>
+          <t>6.32524581166832</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>721.88</t>
+          <t>7.21879384587925</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2433.3</t>
+          <t>24.3330095864962</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2262.93</t>
+          <t>22.6292994842941</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1488.86</t>
+          <t>14.8886258288307</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1495.32</t>
+          <t>14.9531519275066</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1305.03</t>
+          <t>13.0502611528501</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1024.51</t>
+          <t>10.2451339859895</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1205.86</t>
+          <t>12.0585526997076</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>744.35</t>
+          <t>7.44346778145271</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>537.47</t>
+          <t>5.37473717140548</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>447.29</t>
+          <t>4.47286659006391</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>4.15000189525069</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>380.59</t>
+          <t>3.80593114844284</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2039.48</t>
+          <t>20.3948316737812</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2230.31</t>
+          <t>22.3030882333846</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1917.84</t>
+          <t>19.1783641156966</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1876.78</t>
+          <t>18.7678308482706</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1856.58</t>
+          <t>18.5657869990881</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1845.66</t>
+          <t>18.4566396940521</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1817.1</t>
+          <t>18.1710066015523</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1807.26</t>
+          <t>18.0726069388366</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1695.37</t>
+          <t>16.9536607505105</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1651.8</t>
+          <t>16.5179838675117</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1507.2</t>
+          <t>15.0719724831231</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>1414.39</t>
+          <t>14.1439002339567</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>1269.41</t>
+          <t>12.6941039334759</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>1274.81</t>
+          <t>12.7481125790165</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1188.11</t>
+          <t>11.8811044711881</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>0.0184167944626874</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>0.0163351727254157</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-0.0246780964599774</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.00182854184087933</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>0.0452273180163099</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>0.110377803398973</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>0.0226973257919043</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-6.12</t>
+          <t>-0.0612426548066504</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-22.83</t>
+          <t>-0.228306134201927</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-26.99</t>
+          <t>-0.269860264788863</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>-29.5</t>
+          <t>-0.294999440013651</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>-34.67</t>
+          <t>-0.346660732183963</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>-36.14</t>
+          <t>-0.361400042929956</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>-39.7</t>
+          <t>-0.39704635280147</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>-37.6</t>
+          <t>-0.375992947568003</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-34.21</t>
+          <t>-0.34211326550709</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-40.74</t>
+          <t>-0.407390891983594</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-39.05</t>
+          <t>-0.390498527645405</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-35.47</t>
+          <t>-0.354730693108629</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-30</t>
+          <t>-0.299984011902353</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-23.64</t>
+          <t>-0.23644331439002</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-21.83</t>
+          <t>-0.218314350774891</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-24.53</t>
+          <t>-0.245258626972327</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-31.12</t>
+          <t>-0.311198473182029</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-36.24</t>
+          <t>-0.362440575972876</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-32.44</t>
+          <t>-0.324420370106515</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-29.53</t>
+          <t>-0.295342034660592</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-27.22</t>
+          <t>-0.272202534834456</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-27.27</t>
+          <t>-0.272680501957165</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-28.89</t>
+          <t>-0.28891184474879</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-48.01</t>
+          <t>-0.480070672228191</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-37.3</t>
+          <t>-0.372956202692721</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>-31.7</t>
+          <t>-0.316970369984686</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-26.24</t>
+          <t>-0.262413053702971</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-32.39</t>
+          <t>-0.323866305978014</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-34.94</t>
+          <t>-0.349386927605038</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-28.33</t>
+          <t>-0.283250045172117</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-25.22</t>
+          <t>-0.252214781122492</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>-25.15</t>
+          <t>-0.251508286472921</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-25.42</t>
+          <t>-0.25416832361564</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>-21.68</t>
+          <t>-0.216794001492017</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>-13.19</t>
+          <t>-0.131887558489813</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-0.0387641480466465</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>-9.59</t>
+          <t>-0.0959277573647993</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>-21.26</t>
+          <t>-0.212560643028769</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>81.66</t>
+          <t>0.816627414510093</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>72.35</t>
+          <t>0.723503148962235</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>0.894186762130316</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>177.17</t>
+          <t>1.77171893609518</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>149.87</t>
+          <t>1.49867330008533</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>127.59</t>
+          <t>1.27590821954831</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>131.23</t>
+          <t>1.31228663280301</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>122.52</t>
+          <t>1.22516388126279</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>107.28</t>
+          <t>1.07282060733404</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>117.46</t>
+          <t>1.17458847395536</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>86.1</t>
+          <t>0.861000247669437</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>74.21</t>
+          <t>0.742064960902524</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>74.08</t>
+          <t>0.74079504128899</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>106.61</t>
+          <t>1.06611230240695</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>122.69</t>
+          <t>1.22692866380969</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1093.73</t>
+          <t>10.9373346409289</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>817.95</t>
+          <t>8.17946534448587</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>634.35</t>
+          <t>6.34347806402666</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>508.61</t>
+          <t>5.08611301138489</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>506.21</t>
+          <t>5.06213506205196</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>569.61</t>
+          <t>5.69606638962269</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>519.3</t>
+          <t>5.19295335428975</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>436.94</t>
+          <t>4.36935485556181</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>357.38</t>
+          <t>3.57379550290586</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>300.98</t>
+          <t>3.009754389672</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>292.99</t>
+          <t>2.92990537614582</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>248.11</t>
+          <t>2.48114755457735</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>224.72</t>
+          <t>2.24715777978389</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>184.59</t>
+          <t>1.84594086537064</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>217.22</t>
+          <t>2.17215700517948</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>-45.22</t>
+          <t>-0.452178594731455</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-43.76</t>
+          <t>-0.437642452880202</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>-36.64</t>
+          <t>-0.366383876302921</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-40.51</t>
+          <t>-0.405138594183795</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-40.31</t>
+          <t>-0.403054266080141</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-38.45</t>
+          <t>-0.384544966753025</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-40.82</t>
+          <t>-0.408225675741583</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-44.76</t>
+          <t>-0.447627809092666</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>-48.63</t>
+          <t>-0.486277523948645</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-53.1</t>
+          <t>-0.530988631989702</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>-52.88</t>
+          <t>-0.528752083013032</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>-53.23</t>
+          <t>-0.532251322713086</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>-53.58</t>
+          <t>-0.535794936647827</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>-57.42</t>
+          <t>-0.574212973143901</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>-56.9</t>
+          <t>-0.568963131083463</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>774.38</t>
+          <t>7.74377717555578</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>666.75</t>
+          <t>6.66754888114879</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>589.15</t>
+          <t>5.89145350224992</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>545.18</t>
+          <t>5.45178222226297</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>505.55</t>
+          <t>5.05552202341482</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>483.58</t>
+          <t>4.83575393295623</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>457.37</t>
+          <t>4.57370461809957</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>423.08</t>
+          <t>4.23082826938152</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>376.63</t>
+          <t>3.76628722743334</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>308.52</t>
+          <t>3.08515700262325</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>267.81</t>
+          <t>2.67806760198501</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>210.61</t>
+          <t>2.10606249140873</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>135.52</t>
+          <t>1.3551687525074</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>0.898680024211997</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>112.51</t>
+          <t>1.12514432416942</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>371.34</t>
+          <t>3.71342567293712</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>371.81</t>
+          <t>3.71812860553225</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>298.42</t>
+          <t>2.98415047167592</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>266.74</t>
+          <t>2.66735977579821</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>238.4</t>
+          <t>2.38402708009843</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>190.61</t>
+          <t>1.90614125533486</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>163.2</t>
+          <t>1.63198717081729</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>161.26</t>
+          <t>1.61258382067421</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>187.58</t>
+          <t>1.87575641282125</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>222.11</t>
+          <t>2.22108120250063</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>244.87</t>
+          <t>2.44869198869428</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>225.85</t>
+          <t>2.2585056453885</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>239.66</t>
+          <t>2.3966224949924</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>270.51</t>
+          <t>2.70511139722244</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>331.48</t>
+          <t>3.31475671648933</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>64.05</t>
+          <t>0.640529919255068</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>53.36</t>
+          <t>0.533617976314131</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>53.63</t>
+          <t>0.536280994976895</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>47.79</t>
+          <t>0.47793506564853</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>50.94</t>
+          <t>0.509439187209727</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>58.68</t>
+          <t>0.586837819722745</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>0.254891174697205</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>37.46</t>
+          <t>0.374616184492265</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>48.83</t>
+          <t>0.488311157306391</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>20.78</t>
+          <t>0.207807130614602</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>0.194867186940659</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>19.27</t>
+          <t>0.19265219914381</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>0.175972084374396</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>0.0977202708596596</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>0.0806876510689012</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-38.35</t>
+          <t>-0.383460803134186</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-33.8</t>
+          <t>-0.338032686992748</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-27.47</t>
+          <t>-0.2747075735585</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-29.8</t>
+          <t>-0.29801340568477</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-26.48</t>
+          <t>-0.264777344960133</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-21.98</t>
+          <t>-0.219751969857201</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-26.1</t>
+          <t>-0.26096933674546</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-32.32</t>
+          <t>-0.323235471745383</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-38.42</t>
+          <t>-0.384237844637158</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-44.32</t>
+          <t>-0.443188992767044</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-42.69</t>
+          <t>-0.426935418279475</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-42.09</t>
+          <t>-0.420869684194848</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-41.47</t>
+          <t>-0.414705911734787</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-44.57</t>
+          <t>-0.445650137421178</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-45.26</t>
+          <t>-0.452639987792516</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>233.47</t>
+          <t>2.3347172677547</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>197.85</t>
+          <t>1.9784725368415</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>191.46</t>
+          <t>1.91461525429717</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>170.87</t>
+          <t>1.70870646618866</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>201.33</t>
+          <t>2.01334178096901</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>211.63</t>
+          <t>2.11631539749925</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>182.15</t>
+          <t>1.82153626759214</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>177.45</t>
+          <t>1.77446349424479</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>200.14</t>
+          <t>2.00144128793807</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>185.08</t>
+          <t>1.85076650380739</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>162.94</t>
+          <t>1.62936039616379</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>160.91</t>
+          <t>1.60914111640844</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>140.96</t>
+          <t>1.40963135592592</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>110.93</t>
+          <t>1.10931651571879</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>160.26</t>
+          <t>1.60263021625686</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.00460759300288438</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-0.0221637460095382</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-0.0145444443931968</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-6.79</t>
+          <t>-0.0679401692210315</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-3.7</t>
+          <t>-0.0369737386468089</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>0.052044752693996</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>0.0275534179460526</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-0.0422089979926343</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>0.0268883887570912</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-16.87</t>
+          <t>-0.168677237941167</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>-16.42</t>
+          <t>-0.164238151440836</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>-9.25</t>
+          <t>-0.0925011485484414</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>-7.44</t>
+          <t>-0.0744211561848375</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-0.0716152329726454</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-0.073308746534666</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>849.16</t>
+          <t>8.49163676181084</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>892.85</t>
+          <t>8.92845055265296</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>928.98</t>
+          <t>9.28976083241284</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>679.51</t>
+          <t>6.79505416997752</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>802.97</t>
+          <t>8.02973444494252</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>718.77</t>
+          <t>7.18772043550713</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>650.03</t>
+          <t>6.50033580135262</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>633.57</t>
+          <t>6.33567968463532</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>694.22</t>
+          <t>6.94216942334495</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>469.91</t>
+          <t>4.69910190633544</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>326.56</t>
+          <t>3.26562007321148</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>272.82</t>
+          <t>2.72819837205436</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>200.32</t>
+          <t>2.00319493624105</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>157.9</t>
+          <t>1.57900689185157</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>219.83</t>
+          <t>2.19826448586746</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>883.22</t>
+          <t>8.83216618699862</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>723.92</t>
+          <t>7.23917789824051</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>671.34</t>
+          <t>6.71336790256632</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>880.99</t>
+          <t>8.80988631007028</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1750.81</t>
+          <t>17.5080869821024</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1338.39</t>
+          <t>13.3838529372168</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1037.9</t>
+          <t>10.3789529801647</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>857.18</t>
+          <t>8.57181094430946</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>702.91</t>
+          <t>7.02908399347586</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>570.68</t>
+          <t>5.70684891505464</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>452.69</t>
+          <t>4.52691138656945</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>341.72</t>
+          <t>3.41722903001717</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>264.52</t>
+          <t>2.64522004220327</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>173.03</t>
+          <t>1.73034060312605</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>230.01</t>
+          <t>2.30009918911308</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>725.44</t>
+          <t>7.25440779463561</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>616.98</t>
+          <t>6.16976255747323</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>570.37</t>
+          <t>5.70367008202384</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>547.87</t>
+          <t>5.4787446127162</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>613.95</t>
+          <t>6.13947650640552</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>583.43</t>
+          <t>5.83434946104217</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>578.49</t>
+          <t>5.78492928428791</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>507.67</t>
+          <t>5.0767475089081</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>378.6</t>
+          <t>3.78602145863215</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>294.8</t>
+          <t>2.94795591848318</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>261.5</t>
+          <t>2.61498107088651</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>229.19</t>
+          <t>2.29187589740282</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>195.39</t>
+          <t>1.95389686615605</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>148.83</t>
+          <t>1.48826500410652</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>134.1</t>
+          <t>1.3409744239798</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>26.92</t>
+          <t>0.269220549740212</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>31.48</t>
+          <t>0.314760581663249</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>35.27</t>
+          <t>0.352659937421555</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>31.54</t>
+          <t>0.31535600807571</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>40.67</t>
+          <t>0.40673130938471</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>52.77</t>
+          <t>0.527686182201123</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>40.74</t>
+          <t>0.40744131872233</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>33.43</t>
+          <t>0.334334144362053</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>0.160918661710384</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>0.10531264326004</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>11.26</t>
+          <t>0.112624664175644</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>14.58</t>
+          <t>0.14575954381885</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>0.0995681699378781</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>0.0348987632825442</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>0.0328723651948053</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>-24.84</t>
+          <t>-0.248432476466478</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-31.82</t>
+          <t>-0.31823471054011</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>-26.3</t>
+          <t>-0.263047990837952</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-24.31</t>
+          <t>-0.243129326073302</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-19.37</t>
+          <t>-0.193655436518607</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-15.22</t>
+          <t>-0.15222558303851</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-10.93</t>
+          <t>-0.109291979221398</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>-19.12</t>
+          <t>-0.191204510766992</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>-29.87</t>
+          <t>-0.298720092808525</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-33.67</t>
+          <t>-0.336700741684106</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>-31.38</t>
+          <t>-0.3138293524099</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>-29.99</t>
+          <t>-0.299925535016339</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>-31.06</t>
+          <t>-0.310553851033215</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>-29.96</t>
+          <t>-0.299637299250155</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>-22.07</t>
+          <t>-0.220720120432797</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>317.83</t>
+          <t>3.17831574433971</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>277.23</t>
+          <t>2.7722815014902</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>233.22</t>
+          <t>2.33217813788589</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>225.99</t>
+          <t>2.25985426469255</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>175.35</t>
+          <t>1.75345861853491</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>198.42</t>
+          <t>1.98419443568017</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>280.32</t>
+          <t>2.80318968284571</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>312.34</t>
+          <t>3.12344579520419</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>241.43</t>
+          <t>2.4143409233269</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>190.58</t>
+          <t>1.90577601319522</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>172.45</t>
+          <t>1.72453970118539</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>164.77</t>
+          <t>1.6477321055517</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>1.39495883957918</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>133.53</t>
+          <t>1.33527144754501</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>166.97</t>
+          <t>1.66968389939076</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>0.436030220828427</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>0.410486833443713</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>38.04</t>
+          <t>0.380366486150181</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>0.555028435822123</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>54.01</t>
+          <t>0.540111881949467</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>0.466748396976252</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>50.11</t>
+          <t>0.501054162241784</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>60.06</t>
+          <t>0.600647120179025</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>66.83</t>
+          <t>0.66832432193794</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>79.66</t>
+          <t>0.796613322101026</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>80.99</t>
+          <t>0.809850105769537</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>87.66</t>
+          <t>0.876556710447876</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>110.81</t>
+          <t>1.10808602237346</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>124.53</t>
+          <t>1.24525344022691</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>1.30502661286475</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>-23.49</t>
+          <t>-0.23487612570389</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-24.1</t>
+          <t>-0.24095904662953</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>-28.4</t>
+          <t>-0.283976368235254</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-31.42</t>
+          <t>-0.314245948378478</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-31.12</t>
+          <t>-0.311189320985986</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-37.05</t>
+          <t>-0.370461447840922</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>-41.75</t>
+          <t>-0.417512425223964</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>-42.42</t>
+          <t>-0.424209840942178</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>-42.73</t>
+          <t>-0.427264311648819</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-40.61</t>
+          <t>-0.406149480283898</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>-39.99</t>
+          <t>-0.399936456545469</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>-39.98</t>
+          <t>-0.399772960296151</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>-35.24</t>
+          <t>-0.352449488005313</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>-32.88</t>
+          <t>-0.328811650159136</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>-36.47</t>
+          <t>-0.36466676828847</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>154.98</t>
+          <t>1.54981053460458</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>158.99</t>
+          <t>1.5898758737935</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>161.77</t>
+          <t>1.61769016078321</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>169.85</t>
+          <t>1.6985045125717</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>174.31</t>
+          <t>1.74305351523591</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>183.88</t>
+          <t>1.83877395898061</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>201.36</t>
+          <t>2.01361998663343</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>216.11</t>
+          <t>2.16112975840695</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>229.22</t>
+          <t>2.29220687597339</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>231.42</t>
+          <t>2.31423952651203</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>212.85</t>
+          <t>2.12854207161572</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>202.57</t>
+          <t>2.02567454116437</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>208.99</t>
+          <t>2.08994411433474</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>200.3</t>
+          <t>2.00303271101641</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>211.91</t>
+          <t>2.11910225444082</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>25.14</t>
+          <t>0.251394415438399</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>29.22</t>
+          <t>0.292222580871519</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>30.91</t>
+          <t>0.309140744546763</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>0.305653634679999</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>0.331329906898271</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>32.42</t>
+          <t>0.324170938074983</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>34.57</t>
+          <t>0.345714899109803</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>35.99</t>
+          <t>0.359874894817778</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>34.81</t>
+          <t>0.348072272129126</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>37.78</t>
+          <t>0.37783672609627</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>38.84</t>
+          <t>0.388366161904179</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>39.21</t>
+          <t>0.392106378694381</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>43.54</t>
+          <t>0.435388875501731</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>0.454961778521963</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>47.13</t>
+          <t>0.471318276761858</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpPE</t>
